--- a/timetable_generator/timetable_outputs/ECE_Sem3_SectionA_Timetable.xlsx
+++ b/timetable_generator/timetable_outputs/ECE_Sem3_SectionA_Timetable.xlsx
@@ -468,42 +468,40 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MA263
-Random Process
-C101
-Dr. Chinmayananda A</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>MA263
-Random Process
-C101
-Dr. Chinmayananda A</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>EC262
-Semiconductor Devices
-C101
-Dr. Pankaj Kumar</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
           <t>CS307
 Machine Learning
 C101
-Dr. Deepak K.T</t>
+Dr. Deepak K.T
+[COMMON]</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>MA262
+Differential Equations
+C101
+Dr. Anand P Barangi
+[COMMON]</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>CS307
+Machine Learning
+C101
+Dr. Deepak K.T
+[COMMON]</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>EC253
-Introduction to Embedded Signal Intelligence
-C101
-Dr. Sibasankar Padhy</t>
+          <t>MA261
+Multivariable Calculus
+C101
+Dr. Somen B
+[COMMON]
+[TUTORIAL]</t>
         </is>
       </c>
     </row>
@@ -515,35 +513,47 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>MA262
+Differential Equations
+C101
+Dr. Anand P Barangi
+[COMMON]</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>MA263
+Random Process
+C101
+Dr. Chinmayananda A
+[COMMON]</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
           <t>EC262
 Semiconductor Devices
 C101
-Dr. Pankaj Kumar</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>CS307
-Machine Learning
-C101
-Dr. Deepak K.T</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+Dr. Pankaj Kumar
+[COMMON]</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
-        <is>
-          <t>MA262
-Differential Equations
-C101
-Dr. Anand P Barangi</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
         <is>
           <t>MA261
 Multivariable Calculus
 C101
-Dr. Somen B</t>
+Dr. Somen B
+[COMMON]</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>EC262
+Semiconductor Devices
+C101
+Dr. Pankaj Kumar
+[COMMON]</t>
         </is>
       </c>
     </row>
@@ -553,24 +563,45 @@
           <t>Wednesday</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>MA263
+Random Process
+C101
+Dr. Chinmayananda A
+[COMMON]
+[TUTORIAL]</t>
+        </is>
+      </c>
       <c r="C4" t="inlineStr">
-        <is>
-          <t>EC253
-Introduction to Embedded Signal Intelligence
-C101
-Dr. Sibasankar Padhy</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
         <is>
           <t>CS307
 Machine Learning
 C101
-Dr. Deepak K.T</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
+Dr. Deepak K.T
+[COMMON]
+[TUTORIAL]</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>EC262
+Semiconductor Devices
+C101
+Dr. Pankaj Kumar
+[COMMON]</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>MA262
+Differential Equations
+C101
+Dr. Anand P Barangi
+[COMMON]
+[TUTORIAL]</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr"/>
     </row>
     <row r="5">
@@ -579,46 +610,35 @@
           <t>Thursday</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>MA261
-Multivariable Calculus
-C101
-Dr. Somen B</t>
-        </is>
-      </c>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>MA261
-Multivariable Calculus
-C101
-Dr. Somen B</t>
+          <t>EC253
+Introduction to Embedded Signal Intelligence
+C101
+Dr. Sibasankar Padhy
+[COMMON]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
-        <is>
-          <t>MA262
-Differential Equations
-C101
-Dr. Anand P Barangi</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
         <is>
           <t>EC261
 Signal &amp; Systems
 C101
-Dr. Somen B</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>MA262
-Differential Equations
-C101
-Dr. Anand P Barangi</t>
-        </is>
-      </c>
+Dr. Somen B
+[COMMON]</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>MA263
+Random Process
+C101
+Dr. Chinmayananda A
+[COMMON]</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -628,30 +648,34 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MA263
-Random Process
-C101
-Dr. Chinmayananda A</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>EC262
-Semiconductor Devices
-C101
-Dr. Pankaj Kumar</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
+          <t>EC253
+Introduction to Embedded Signal Intelligence
+C101
+Dr. Sibasankar Padhy
+[COMMON]</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>MA261
+Multivariable Calculus
+C101
+Dr. Somen B
+[COMMON]</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
         <is>
           <t>EC261
 Signal &amp; Systems
 C101
-Dr. Somen B</t>
-        </is>
-      </c>
+Dr. Somen B
+[COMMON]
+[TUTORIAL]</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
